--- a/docs/宮城県_推奨変電所リスト_社外提示用(NDA前).xlsx
+++ b/docs/宮城県_推奨変電所リスト_社外提示用(NDA前).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -94,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,11 +108,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -485,6 +495,10 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -550,6 +564,26 @@
           <t>ひとこと</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>緯度</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>経度</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>地図</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -588,6 +622,22 @@
           <t>154kV受電・空容量に余裕。仙台市西部の郊外。市街化調整区域の開発許可の扱いは要確認</t>
         </is>
       </c>
+      <c r="I6" s="4" t="n">
+        <v>38.2953</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>140.81855</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -626,6 +676,22 @@
           <t>空容量に余裕。名取市西部で周辺に農地が多く、用地を探しやすい見込み</t>
         </is>
       </c>
+      <c r="I7" s="4" t="n">
+        <v>38.1965</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>140.85948</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -664,6 +730,22 @@
           <t>空容量に余裕。周辺は農地中心で用地を探しやすい見込み</t>
         </is>
       </c>
+      <c r="I8" s="4" t="n">
+        <v>38.06467</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>140.73261</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -702,6 +784,22 @@
           <t>空容量に余裕。仙台近郊でアクセス良好</t>
         </is>
       </c>
+      <c r="I9" s="4" t="n">
+        <v>38.34288</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>140.96028</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -740,6 +838,22 @@
           <t>空容量に余裕。沿岸部のため津波浸水想定の確認が必要</t>
         </is>
       </c>
+      <c r="I10" s="4" t="n">
+        <v>38.16293</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>140.9074</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -778,6 +892,22 @@
           <t>空容量に余裕。大崎市古川の郊外</t>
         </is>
       </c>
+      <c r="I11" s="4" t="n">
+        <v>38.56297</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>140.96517</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -816,6 +946,22 @@
           <t>空容量に余裕。仙台北部の郊外</t>
         </is>
       </c>
+      <c r="I12" s="4" t="n">
+        <v>38.37769</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>140.88093</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -854,658 +1000,963 @@
           <t>空容量あり。周辺は農地中心。津波浸水想定の確認が必要</t>
         </is>
       </c>
+      <c r="I13" s="4" t="n">
+        <v>38.12392</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>140.90055</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>福田町変電所</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>仙台市宮城野区扇町四丁目</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>工業地</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>空容量が大きい。工業地で用途地域面は有利だが用地単価は高め</t>
         </is>
       </c>
+      <c r="I14" s="6" t="n">
+        <v>38.26078</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>140.94899</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>重吉変電所</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>石巻市重吉町</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>港湾・工業地</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>空容量が大きい。石巻港周辺。津波浸水想定の確認が必要</t>
         </is>
       </c>
+      <c r="I15" s="6" t="n">
+        <v>38.42074</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>141.26503</v>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>卸町変電所</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>仙台市若林区卸町一丁目</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>流通業務地</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>空容量が大きい。用地単価は高め</t>
         </is>
       </c>
+      <c r="I16" s="6" t="n">
+        <v>38.25249</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>140.92042</v>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>新浜変電所</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>塩竈市新浜町二丁目</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>港湾・工業地</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>空容量が大きい。塩釜港周辺。津波浸水想定の確認が必要</t>
         </is>
       </c>
+      <c r="I17" s="6" t="n">
+        <v>38.33187</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>141.03958</v>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>目安（要現地確認）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>明通変電所</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>仙台市泉区明通一丁目</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>154kV</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>市街地（泉区）</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>154kV受電・空容量が大きい。用地単価は高め</t>
         </is>
       </c>
+      <c r="I18" s="6" t="n">
+        <v>38.34855</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>140.86163</v>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>石巻湊変電所</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>石巻市湊</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>港湾・市街地</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>空容量が大きい。津波浸水想定の確認が必要</t>
         </is>
       </c>
+      <c r="I19" s="6" t="n">
+        <v>38.42532</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>141.32433</v>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>塩釜築港変電所</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>塩竈市舟入一丁目</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>港湾・工業地</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>空容量あり。津波浸水想定の確認が必要</t>
         </is>
       </c>
+      <c r="I20" s="6" t="n">
+        <v>38.31248</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>141.03088</v>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>岩沼変電所</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>岩沼市桑原一丁目</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>市街地寄り</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>空容量に余裕。周辺は市街地のため用地は郊外側で探す想定</t>
         </is>
       </c>
+      <c r="I21" s="6" t="n">
+        <v>38.1026</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>140.8606</v>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>陸前山下変電所</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>石巻市西山町</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>市街地寄り</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>空容量あり。石巻市西部</t>
         </is>
       </c>
+      <c r="I22" s="6" t="n">
+        <v>38.43492</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>141.29238</v>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>船岡変電所</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>柴田町船岡新栄一丁目</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>市街地寄り</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>空容量あり。柴田町</t>
         </is>
       </c>
+      <c r="I23" s="6" t="n">
+        <v>38.05913</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>140.78154</v>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>成田変電所</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>富谷市成田八丁目</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>住宅地</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>空容量あり。周辺は住宅地のため用地確保に工夫が必要</t>
         </is>
       </c>
+      <c r="I24" s="6" t="n">
+        <v>38.35967</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>140.89219</v>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>目安（要現地確認）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>蛇田変電所</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>石巻市のぞみ野三丁目</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>住宅地</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>空容量あり。石巻市の住宅地</t>
         </is>
       </c>
+      <c r="I25" s="6" t="n">
+        <v>38.44884</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>141.26008</v>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>吉岡変電所</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>大和町吉岡</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>郊外</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>空容量あり。大和町中心部の近く</t>
         </is>
       </c>
+      <c r="I26" s="6" t="n">
+        <v>38.44293</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>140.89674</v>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>増田変電所</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>名取市手倉田</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>市街地寄り</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>空容量あり。名取市中心部の近く</t>
         </is>
       </c>
+      <c r="I27" s="6" t="n">
+        <v>38.17185</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>140.88113</v>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>涌谷変電所</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>涌谷町字渋江</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>農村部</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>空容量あり。周辺は農地中心</t>
         </is>
       </c>
+      <c r="I28" s="6" t="n">
+        <v>38.53834</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>141.12049</v>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>佐沼変電所</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>登米市迫町佐沼</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>66kV</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>市街地寄り</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>空容量あり。登米市中心部の近く</t>
         </is>
       </c>
+      <c r="I29" s="6" t="n">
+        <v>38.68661</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>141.20365</v>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>地図で開く</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>【ご留意事項】</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>・本リストは公表情報をもとにした机上の一次スクリーニングです。連系の可否・負担金・工期は一般送配電事業者の接続検討で確定します。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>・空容量は公表時点の値で、先行申込により変動します。最新値は東北電力ネットワークの空容量マップでご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>・宮城県内の該当変電所は、いずれもN-1電制「不可」・出力制御「あり」の公表条件です。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>・立地区分は所在地からの推定で、現地・用途地域・ハザード（津波浸水等）は未確認です。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>・緯度経度は地図データ（OpenStreetMap等）から当社が取得した変電所の位置です。「確認済」は地図上の変電所設備と一致したもの、「目安」は名称検索による位置で数百m〜数kmずれる可能性があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>・具体的な候補地・接続検討の実績等の詳細は、秘密保持契約の締結後にご案内いたします。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/宮城県_推奨変電所リスト_社外提示用(NDA前).xlsx
+++ b/docs/宮城県_推奨変電所リスト_社外提示用(NDA前).xlsx
@@ -49,7 +49,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -64,11 +64,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,12 +104,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -484,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -518,7 +507,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>◎=おすすめ（空容量に余裕があり郊外で用地を探しやすい） ○=候補（空容量はあるが市街地・工業地・沿岸部など条件付き）</t>
+          <t>掲載基準：空容量に余裕があり、郊外で蓄電所用地を探しやすい変電所</t>
         </is>
       </c>
     </row>
@@ -1017,914 +1006,50 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>福田町変電所</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>仙台市宮城野区扇町四丁目</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>工業地</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>空容量が大きい。工業地で用途地域面は有利だが用地単価は高め</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>38.26078</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>140.94899</v>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>重吉変電所</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>石巻市重吉町</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>港湾・工業地</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>空容量が大きい。石巻港周辺。津波浸水想定の確認が必要</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>38.42074</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>141.26503</v>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>【ご留意事項】</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>卸町変電所</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>仙台市若林区卸町一丁目</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>流通業務地</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>空容量が大きい。用地単価は高め</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>38.25249</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>140.92042</v>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>・本リストは公表情報をもとにした机上の一次スクリーニングです。連系の可否・負担金・工期は一般送配電事業者の接続検討で確定します。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>新浜変電所</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>塩竈市新浜町二丁目</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>港湾・工業地</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>空容量が大きい。塩釜港周辺。津波浸水想定の確認が必要</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>38.33187</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>141.03958</v>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>目安（要現地確認）</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>・空容量は公表時点の値で、先行申込により変動します。最新値は東北電力ネットワークの空容量マップでご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>明通変電所</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>仙台市泉区明通一丁目</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>154kV</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>市街地（泉区）</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>154kV受電・空容量が大きい。用地単価は高め</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>38.34855</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>140.86163</v>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>・宮城県内の該当変電所は、いずれもN-1電制「不可」・出力制御「あり」の公表条件です。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>石巻湊変電所</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>石巻市湊</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>港湾・市街地</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>空容量が大きい。津波浸水想定の確認が必要</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>38.42532</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>141.32433</v>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>・立地区分は所在地からの推定で、現地・用途地域・ハザード（津波浸水等）は未確認です。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>塩釜築港変電所</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>塩竈市舟入一丁目</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>港湾・工業地</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。津波浸水想定の確認が必要</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>38.31248</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>141.03088</v>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>・緯度経度は地図データ（OpenStreetMap等）から当社が取得した変電所の位置です。「確認済」は地図上の変電所設備と一致したものです。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>岩沼変電所</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>岩沼市桑原一丁目</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>市街地寄り</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>空容量に余裕。周辺は市街地のため用地は郊外側で探す想定</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>38.1026</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>140.8606</v>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>陸前山下変電所</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>石巻市西山町</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>市街地寄り</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。石巻市西部</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>38.43492</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>141.29238</v>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>船岡変電所</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>柴田町船岡新栄一丁目</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>市街地寄り</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。柴田町</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>38.05913</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>140.78154</v>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>成田変電所</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>富谷市成田八丁目</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>住宅地</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。周辺は住宅地のため用地確保に工夫が必要</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>38.35967</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>140.89219</v>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>目安（要現地確認）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>蛇田変電所</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>石巻市のぞみ野三丁目</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>住宅地</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。石巻市の住宅地</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>38.44884</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>141.26008</v>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>吉岡変電所</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>大和町吉岡</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>郊外</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。大和町中心部の近く</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>38.44293</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>140.89674</v>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>増田変電所</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>名取市手倉田</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>市街地寄り</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。名取市中心部の近く</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>38.17185</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>140.88113</v>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>涌谷変電所</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>涌谷町字渋江</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>農村部</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。周辺は農地中心</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>38.53834</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>141.12049</v>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>佐沼変電所</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>登米市迫町佐沼</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>66kV</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>市街地寄り</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>空容量あり。登米市中心部の近く</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>38.68661</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>141.20365</v>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>地図で開く</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>【ご留意事項】</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>・本リストは公表情報をもとにした机上の一次スクリーニングです。連系の可否・負担金・工期は一般送配電事業者の接続検討で確定します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>・空容量は公表時点の値で、先行申込により変動します。最新値は東北電力ネットワークの空容量マップでご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>・宮城県内の該当変電所は、いずれもN-1電制「不可」・出力制御「あり」の公表条件です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>・立地区分は所在地からの推定で、現地・用途地域・ハザード（津波浸水等）は未確認です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>・緯度経度は地図データ（OpenStreetMap等）から当社が取得した変電所の位置です。「確認済」は地図上の変電所設備と一致したもの、「目安」は名称検索による位置で数百m〜数kmずれる可能性があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>・具体的な候補地・接続検討の実績等の詳細は、秘密保持契約の締結後にご案内いたします。</t>
         </is>
@@ -1940,22 +1065,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/docs/宮城県_推奨変電所リスト_社外提示用(NDA前).xlsx
+++ b/docs/宮城県_推奨変電所リスト_社外提示用(NDA前).xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>作成日 2026-09-30 ／ 空容量は東北電力ネットワークの公表値（当社調べ・2026-08-18時点）</t>
+          <t>作成日 2026-09-30 ／ 空容量は東北電力ネットワーク公表「変電所の予想潮流等一覧表」（2026年7月3日作成版）の空容量(当該設備)</t>
         </is>
       </c>
     </row>
